--- a/كاركرد/تير و مرداد 1405/فرمت صورتحساب فروش كالا و  خدمات.xlsx
+++ b/كاركرد/تير و مرداد 1405/فرمت صورتحساب فروش كالا و  خدمات.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\10680684\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\SamandTarabar\st-transport-docs\كاركرد\تير و مرداد 1405\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0BCFC42-7C00-4CA3-B0BB-A8306FA1C936}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3304BCAF-146A-4E42-B980-F535F7E908E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -274,7 +274,7 @@
             <a:rPr lang="fa-IR" sz="1100">
               <a:cs typeface="B Nazanin" panose="00000400000000000000" pitchFamily="2" charset="-78"/>
             </a:rPr>
-            <a:t>شماره سريال: 140411005</a:t>
+            <a:t>شماره سريال: 140503027</a:t>
           </a:r>
           <a:br>
             <a:rPr lang="fa-IR" sz="1100">
@@ -1940,13 +1940,13 @@
             <a:rPr lang="fa-IR" sz="1400">
               <a:cs typeface="B Nazanin" panose="00000400000000000000" pitchFamily="2" charset="-78"/>
             </a:rPr>
-            <a:t>ششصد</a:t>
+            <a:t>ششصد </a:t>
           </a:r>
           <a:r>
             <a:rPr lang="fa-IR" sz="1400" baseline="0">
               <a:cs typeface="B Nazanin" panose="00000400000000000000" pitchFamily="2" charset="-78"/>
             </a:rPr>
-            <a:t> ميليون ريال</a:t>
+            <a:t>ميليون ريال</a:t>
           </a:r>
           <a:endParaRPr lang="en-US" sz="1100">
             <a:cs typeface="B Nazanin" panose="00000400000000000000" pitchFamily="2" charset="-78"/>
@@ -2107,7 +2107,7 @@
       <xdr:row>6</xdr:row>
       <xdr:rowOff>1225827</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="341632" cy="254557"/>
+    <xdr:ext cx="327654" cy="264560"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="12" name="TextBox 11">
@@ -2121,8 +2121,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9921158442" y="5517680"/>
-          <a:ext cx="341632" cy="254557"/>
+          <a:off x="9921172420" y="5517680"/>
+          <a:ext cx="327654" cy="264560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2151,8 +2151,8 @@
         <a:p>
           <a:pPr algn="r" rtl="1"/>
           <a:r>
-            <a:rPr lang="fa-IR" sz="1100"/>
-            <a:t>60</a:t>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>83</a:t>
           </a:r>
           <a:endParaRPr lang="ar-SA" sz="1100"/>
         </a:p>
@@ -2163,11 +2163,11 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>3589796</xdr:colOff>
+      <xdr:colOff>3623414</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>1208772</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="937380" cy="256737"/>
+      <xdr:rowOff>1208773</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="685124" cy="264560"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="13" name="TextBox 12">
@@ -2181,8 +2181,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9920141824" y="5500625"/>
-          <a:ext cx="937380" cy="256737"/>
+          <a:off x="9920360462" y="5500626"/>
+          <a:ext cx="685124" cy="264560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2204,17 +2204,17 @@
         </a:fontRef>
       </xdr:style>
       <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="1" anchor="t">
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="1" anchor="t">
           <a:spAutoFit/>
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="r" rtl="1"/>
           <a:r>
-            <a:rPr lang="en-US" sz="1050"/>
-            <a:t>10,000,000</a:t>
-          </a:r>
-          <a:endParaRPr lang="ar-SA" sz="1050"/>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>7250000</a:t>
+          </a:r>
+          <a:endParaRPr lang="ar-SA" sz="1100"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -2399,11 +2399,11 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>9693088</xdr:colOff>
+      <xdr:colOff>9898272</xdr:colOff>
       <xdr:row>6</xdr:row>
       <xdr:rowOff>1176617</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1093184" cy="311496"/>
+    <xdr:ext cx="898516" cy="426784"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="17" name="TextBox 16">
@@ -2417,8 +2417,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9913882728" y="5468470"/>
-          <a:ext cx="1093184" cy="311496"/>
+          <a:off x="9913872212" y="5468470"/>
+          <a:ext cx="898516" cy="426784"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2445,11 +2445,41 @@
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="l" defTabSz="914400" rtl="1" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>600,000,000</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1400">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
           <a:pPr algn="l" rtl="1"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1400"/>
-            <a:t>600,000,000</a:t>
-          </a:r>
           <a:endParaRPr lang="ar-SA" sz="1100"/>
         </a:p>
       </xdr:txBody>

--- a/كاركرد/تير و مرداد 1405/فرمت صورتحساب فروش كالا و  خدمات.xlsx
+++ b/كاركرد/تير و مرداد 1405/فرمت صورتحساب فروش كالا و  خدمات.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\SamandTarabar\st-transport-docs\كاركرد\تير و مرداد 1405\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3304BCAF-146A-4E42-B980-F535F7E908E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A63F15C-0B02-4561-AC43-D1AB57633D60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1940,13 +1940,13 @@
             <a:rPr lang="fa-IR" sz="1400">
               <a:cs typeface="B Nazanin" panose="00000400000000000000" pitchFamily="2" charset="-78"/>
             </a:rPr>
-            <a:t>ششصد </a:t>
+            <a:t>ششصد</a:t>
           </a:r>
           <a:r>
             <a:rPr lang="fa-IR" sz="1400" baseline="0">
               <a:cs typeface="B Nazanin" panose="00000400000000000000" pitchFamily="2" charset="-78"/>
             </a:rPr>
-            <a:t>ميليون ريال</a:t>
+            <a:t> و يك ميليون و هفتصد و پنجاه هزار ريال</a:t>
           </a:r>
           <a:endParaRPr lang="en-US" sz="1100">
             <a:cs typeface="B Nazanin" panose="00000400000000000000" pitchFamily="2" charset="-78"/>
@@ -2272,7 +2272,7 @@
           <a:pPr algn="l" rtl="1"/>
           <a:r>
             <a:rPr lang="en-US" sz="1400"/>
-            <a:t>600,000,000</a:t>
+            <a:t>601,750,000</a:t>
           </a:r>
           <a:endParaRPr lang="ar-SA" sz="1100"/>
         </a:p>
@@ -2472,7 +2472,7 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>600,000,000</a:t>
+            <a:t>601,750,000</a:t>
           </a:r>
           <a:endParaRPr lang="en-US" sz="1400">
             <a:effectLst/>
